--- a/artfynd/A 38789-2026 artfynd.xlsx
+++ b/artfynd/A 38789-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137369035</v>
       </c>
       <c r="B2" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137369085</v>
       </c>
       <c r="B3" t="n">
-        <v>99433</v>
+        <v>99435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137369336</v>
       </c>
       <c r="B4" t="n">
-        <v>108448</v>
+        <v>108451</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38789-2026 artfynd.xlsx
+++ b/artfynd/A 38789-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137369035</v>
       </c>
       <c r="B2" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137369085</v>
       </c>
       <c r="B3" t="n">
-        <v>99435</v>
+        <v>99441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137369336</v>
       </c>
       <c r="B4" t="n">
-        <v>108451</v>
+        <v>108457</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38789-2026 artfynd.xlsx
+++ b/artfynd/A 38789-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137369336</v>
       </c>
       <c r="B4" t="n">
-        <v>108457</v>
+        <v>108458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38789-2026 artfynd.xlsx
+++ b/artfynd/A 38789-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137369035</v>
       </c>
       <c r="B2" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137369085</v>
       </c>
       <c r="B3" t="n">
-        <v>99441</v>
+        <v>99453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137369336</v>
       </c>
       <c r="B4" t="n">
-        <v>108458</v>
+        <v>108470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38789-2026 artfynd.xlsx
+++ b/artfynd/A 38789-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137369035</v>
       </c>
       <c r="B2" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137369085</v>
       </c>
       <c r="B3" t="n">
-        <v>99453</v>
+        <v>99454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137369336</v>
       </c>
       <c r="B4" t="n">
-        <v>108470</v>
+        <v>108471</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38789-2026 artfynd.xlsx
+++ b/artfynd/A 38789-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137369035</v>
       </c>
       <c r="B2" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137369085</v>
       </c>
       <c r="B3" t="n">
-        <v>99454</v>
+        <v>99457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137369336</v>
       </c>
       <c r="B4" t="n">
-        <v>108471</v>
+        <v>108474</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38789-2026 artfynd.xlsx
+++ b/artfynd/A 38789-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137369035</v>
       </c>
       <c r="B2" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137369085</v>
       </c>
       <c r="B3" t="n">
-        <v>99457</v>
+        <v>99461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137369336</v>
       </c>
       <c r="B4" t="n">
-        <v>108474</v>
+        <v>108480</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
